--- a/QUOTATION_EXCEL_TEMPLATES/kh_la_land/KH_LA_LAND_2026_QUOTATION.xlsx
+++ b/QUOTATION_EXCEL_TEMPLATES/kh_la_land/KH_LA_LAND_2026_QUOTATION.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\수정 임시 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\QUOTATION_EXCEL_TEMPLATES\kh_la_land\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6439610-8190-4C00-9DA4-E790A6BBB942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4090F71-CB7C-4C8F-882E-9EF7471697E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="0" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1005" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -1354,16 +1354,16 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Cambodia-Lao Trucking 거래 명세서</t>
+    <t>LKCBL 2026xx-xx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBL10-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cambodia-Lao Trucking 가견적서</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>LKCBL 2026xx-xx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CBL10-01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2317,43 +2317,76 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2386,97 +2419,64 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3154,7 +3154,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1125"/>
+                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1126"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3520,19 +3520,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="G1" s="172" t="s">
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="G1" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="36" t="s">
@@ -3567,24 +3567,24 @@
         <f>B3+C3</f>
         <v>24000</v>
       </c>
-      <c r="G3" s="173" t="s">
+      <c r="G3" s="170" t="s">
         <v>215</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="M3" s="173" t="s">
+      <c r="H3" s="170"/>
+      <c r="I3" s="170"/>
+      <c r="J3" s="170"/>
+      <c r="M3" s="170" t="s">
         <v>186</v>
       </c>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="173"/>
-      <c r="T3" s="173" t="s">
+      <c r="N3" s="170"/>
+      <c r="O3" s="170"/>
+      <c r="P3" s="170"/>
+      <c r="T3" s="170" t="s">
         <v>187</v>
       </c>
-      <c r="U3" s="173"/>
-      <c r="V3" s="173"/>
-      <c r="W3" s="173"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="40" t="s">
@@ -3600,31 +3600,31 @@
         <f>B4+C4</f>
         <v>34</v>
       </c>
-      <c r="G4" s="174" t="s">
+      <c r="G4" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="175"/>
-      <c r="I4" s="174" t="s">
+      <c r="H4" s="172"/>
+      <c r="I4" s="171" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="175"/>
+      <c r="J4" s="172"/>
       <c r="K4" s="49"/>
-      <c r="M4" s="174" t="s">
+      <c r="M4" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="N4" s="175"/>
-      <c r="O4" s="174" t="s">
+      <c r="N4" s="172"/>
+      <c r="O4" s="171" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="175"/>
-      <c r="T4" s="174" t="s">
+      <c r="P4" s="172"/>
+      <c r="T4" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="175"/>
-      <c r="V4" s="174" t="s">
+      <c r="U4" s="172"/>
+      <c r="V4" s="171" t="s">
         <v>64</v>
       </c>
-      <c r="W4" s="175"/>
+      <c r="W4" s="172"/>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="42" t="s">
@@ -4209,10 +4209,10 @@
       <c r="X17" s="61"/>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="169"/>
-      <c r="B18" s="169"/>
-      <c r="C18" s="169"/>
-      <c r="D18" s="169"/>
+      <c r="A18" s="173"/>
+      <c r="B18" s="173"/>
+      <c r="C18" s="173"/>
+      <c r="D18" s="173"/>
       <c r="G18" s="36" t="s">
         <v>225</v>
       </c>
@@ -4249,12 +4249,12 @@
       <c r="X18" s="61"/>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="169" t="s">
+      <c r="A19" s="173" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="169"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="169"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
       <c r="G19" s="36" t="s">
         <v>101</v>
       </c>
@@ -4344,11 +4344,11 @@
       </c>
       <c r="Q21" s="61"/>
       <c r="R21" s="61"/>
-      <c r="T21" s="170" t="s">
+      <c r="T21" s="169" t="s">
         <v>138</v>
       </c>
-      <c r="U21" s="170"/>
-      <c r="V21" s="170"/>
+      <c r="U21" s="169"/>
+      <c r="V21" s="169"/>
       <c r="W21" s="61">
         <f>SUM(W9:W20)</f>
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="Q24" s="61"/>
       <c r="R24" s="61"/>
-      <c r="T24" s="173" t="s">
+      <c r="T24" s="170" t="s">
         <v>188</v>
       </c>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
+      <c r="U24" s="170"/>
+      <c r="V24" s="170"/>
+      <c r="W24" s="170"/>
       <c r="X24" s="35"/>
     </row>
     <row r="25" spans="1:24">
@@ -4755,11 +4755,11 @@
       </c>
       <c r="Q32" s="61"/>
       <c r="R32" s="61"/>
-      <c r="T32" s="170" t="s">
+      <c r="T32" s="169" t="s">
         <v>138</v>
       </c>
-      <c r="U32" s="170"/>
-      <c r="V32" s="170"/>
+      <c r="U32" s="169"/>
+      <c r="V32" s="169"/>
       <c r="W32" s="61">
         <f>SUM(W26:W31)</f>
         <v>0</v>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="J46" s="51"/>
       <c r="K46" s="51"/>
-      <c r="M46" s="170" t="s">
+      <c r="M46" s="169" t="s">
         <v>297</v>
       </c>
-      <c r="N46" s="170"/>
-      <c r="O46" s="170"/>
-      <c r="P46" s="170"/>
+      <c r="N46" s="169"/>
+      <c r="O46" s="169"/>
+      <c r="P46" s="169"/>
       <c r="Q46" s="51">
         <f>SUM(Q9:Q45)</f>
         <v>0</v>
@@ -5277,11 +5277,11 @@
       <c r="K58" s="51"/>
     </row>
     <row r="59" spans="7:11">
-      <c r="G59" s="170" t="s">
+      <c r="G59" s="169" t="s">
         <v>138</v>
       </c>
-      <c r="H59" s="170"/>
-      <c r="I59" s="170"/>
+      <c r="H59" s="169"/>
+      <c r="I59" s="169"/>
       <c r="J59" s="54">
         <f>SUM(J9:J58)</f>
         <v>0</v>
@@ -5309,6 +5309,11 @@
     </sortState>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:K1"/>
     <mergeCell ref="T21:V21"/>
     <mergeCell ref="G59:I59"/>
     <mergeCell ref="G3:J3"/>
@@ -5322,11 +5327,6 @@
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="T24:W24"/>
     <mergeCell ref="T32:V32"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="M46:P46"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="G1:K1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5551,24 +5551,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="139" t="s">
-        <v>331</v>
-      </c>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
+      <c r="C1" s="150" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
       <c r="L1" s="85" t="s">
         <v>253</v>
       </c>
-      <c r="M1" s="135" t="s">
-        <v>332</v>
-      </c>
-      <c r="N1" s="136"/>
+      <c r="M1" s="146" t="s">
+        <v>331</v>
+      </c>
+      <c r="N1" s="147"/>
       <c r="R1" s="23">
         <f>D11</f>
         <v>1</v>
@@ -5597,22 +5597,22 @@
       <c r="D2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="137" t="s">
+      <c r="E2" s="148" t="s">
         <v>321</v>
       </c>
-      <c r="F2" s="137"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="122" t="s">
+      <c r="F2" s="148"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="156" t="s">
         <v>185</v>
       </c>
-      <c r="J2" s="123"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="131" t="s">
+      <c r="J2" s="157"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="165" t="s">
         <v>239</v>
       </c>
-      <c r="M2" s="132"/>
-      <c r="N2" s="143"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="154"/>
       <c r="R2" s="24">
         <f>N16</f>
         <v>0</v>
@@ -5645,12 +5645,12 @@
       <c r="F3" s="121"/>
       <c r="G3" s="121"/>
       <c r="H3" s="121"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="144"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="167"/>
+      <c r="M3" s="168"/>
+      <c r="N3" s="155"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -5682,16 +5682,16 @@
       <c r="F4" s="121"/>
       <c r="G4" s="121"/>
       <c r="H4" s="121"/>
-      <c r="I4" s="128" t="s">
+      <c r="I4" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="129"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="140" t="s">
+      <c r="J4" s="163"/>
+      <c r="K4" s="164"/>
+      <c r="L4" s="151" t="s">
         <v>240</v>
       </c>
-      <c r="M4" s="141"/>
-      <c r="N4" s="142"/>
+      <c r="M4" s="152"/>
+      <c r="N4" s="153"/>
       <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C6" s="67">
         <f>VLOOKUP(MAX(E6,J6),'Row data'!$B$8:$C$19,2,TRUE)</f>
@@ -5898,21 +5898,21 @@
       <c r="N11" s="13"/>
     </row>
     <row r="12" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A12" s="163" t="s">
+      <c r="A12" s="122" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="163"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163" t="s">
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122" t="s">
         <v>219</v>
       </c>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
       <c r="L12" s="121" t="s">
         <v>15</v>
       </c>
@@ -5924,19 +5924,19 @@
       <c r="P12" s="23"/>
     </row>
     <row r="13" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A13" s="164" t="s">
+      <c r="A13" s="123" t="s">
         <v>320</v>
       </c>
-      <c r="B13" s="165"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
       <c r="L13" s="89" t="s">
         <v>16</v>
       </c>
@@ -5950,17 +5950,17 @@
       </c>
     </row>
     <row r="14" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A14" s="165"/>
-      <c r="B14" s="165"/>
-      <c r="C14" s="165"/>
-      <c r="D14" s="165"/>
-      <c r="E14" s="165"/>
-      <c r="F14" s="166"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="166"/>
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="166"/>
+      <c r="A14" s="124"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
       <c r="L14" s="89" t="s">
         <v>254</v>
       </c>
@@ -5974,17 +5974,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A15" s="165"/>
-      <c r="B15" s="165"/>
-      <c r="C15" s="165"/>
-      <c r="D15" s="165"/>
-      <c r="E15" s="165"/>
-      <c r="F15" s="166"/>
-      <c r="G15" s="166"/>
-      <c r="H15" s="166"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="166"/>
+      <c r="A15" s="124"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
       <c r="L15" s="89" t="s">
         <v>255</v>
       </c>
@@ -5998,18 +5998,18 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A16" s="165"/>
-      <c r="B16" s="165"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="165"/>
-      <c r="F16" s="166"/>
-      <c r="G16" s="166"/>
-      <c r="H16" s="166"/>
-      <c r="I16" s="166"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="166"/>
-      <c r="L16" s="167" t="s">
+      <c r="A16" s="124"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="125"/>
+      <c r="K16" s="125"/>
+      <c r="L16" s="126" t="s">
         <v>220</v>
       </c>
       <c r="M16" s="86" t="s">
@@ -6021,18 +6021,18 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A17" s="165"/>
-      <c r="B17" s="165"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="165"/>
-      <c r="E17" s="165"/>
-      <c r="F17" s="166"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
-      <c r="L17" s="168"/>
+      <c r="A17" s="124"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="125"/>
+      <c r="K17" s="125"/>
+      <c r="L17" s="127"/>
       <c r="M17" s="87" t="s">
         <v>18</v>
       </c>
@@ -6042,18 +6042,18 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A18" s="165"/>
-      <c r="B18" s="165"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="165"/>
-      <c r="E18" s="165"/>
-      <c r="F18" s="166"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="168"/>
+      <c r="A18" s="124"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="127"/>
       <c r="M18" s="88" t="s">
         <v>19</v>
       </c>
@@ -6063,18 +6063,18 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A19" s="165"/>
-      <c r="B19" s="165"/>
-      <c r="C19" s="165"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="166"/>
-      <c r="G19" s="166"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="166"/>
-      <c r="L19" s="168"/>
+      <c r="A19" s="124"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="127"/>
       <c r="M19" s="14" t="s">
         <v>20</v>
       </c>
@@ -6100,65 +6100,65 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="146" t="s">
+      <c r="A21" s="129" t="s">
         <v>330</v>
       </c>
-      <c r="B21" s="146"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="146"/>
-      <c r="G21" s="146"/>
-      <c r="H21" s="146"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="146"/>
-      <c r="L21" s="146"/>
-      <c r="M21" s="146"/>
-      <c r="N21" s="146"/>
+      <c r="B21" s="129"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="129"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="129"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A22" s="147" t="s">
+      <c r="A22" s="130" t="s">
         <v>222</v>
       </c>
-      <c r="B22" s="147"/>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="147"/>
-      <c r="F22" s="147"/>
-      <c r="G22" s="147"/>
-      <c r="H22" s="147"/>
-      <c r="I22" s="147"/>
-      <c r="J22" s="147"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="147"/>
-      <c r="M22" s="147"/>
-      <c r="N22" s="147"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
+      <c r="M22" s="130"/>
+      <c r="N22" s="130"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A23" s="147"/>
-      <c r="B23" s="147"/>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="147"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="147"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="147"/>
-      <c r="K23" s="147"/>
-      <c r="L23" s="147"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="147"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="130"/>
+      <c r="N23" s="130"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A24" s="148" t="s">
+      <c r="A24" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="149"/>
-      <c r="C24" s="154"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="156"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="139"/>
       <c r="F24" s="26"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
@@ -6167,73 +6167,73 @@
       <c r="K24" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="145"/>
-      <c r="M24" s="145"/>
-      <c r="N24" s="145"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A25" s="150"/>
-      <c r="B25" s="151"/>
-      <c r="C25" s="157"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="159"/>
+      <c r="A25" s="133"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="142"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="121"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="145"/>
-      <c r="N25" s="145"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="128"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A26" s="150"/>
-      <c r="B26" s="151"/>
-      <c r="C26" s="157"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="159"/>
+      <c r="A26" s="133"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="142"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="121"/>
-      <c r="L26" s="145"/>
-      <c r="M26" s="145"/>
-      <c r="N26" s="145"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="128"/>
+      <c r="N26" s="128"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A27" s="150"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="157"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="159"/>
+      <c r="A27" s="133"/>
+      <c r="B27" s="134"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="142"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
       <c r="K27" s="121"/>
-      <c r="L27" s="145"/>
-      <c r="M27" s="145"/>
-      <c r="N27" s="145"/>
+      <c r="L27" s="128"/>
+      <c r="M27" s="128"/>
+      <c r="N27" s="128"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A28" s="152"/>
-      <c r="B28" s="153"/>
-      <c r="C28" s="160"/>
-      <c r="D28" s="161"/>
-      <c r="E28" s="162"/>
+      <c r="A28" s="135"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="143"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="145"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="121"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="145"/>
-      <c r="N28" s="145"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="128"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="3"/>
@@ -6322,12 +6322,19 @@
     <row r="62" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E19"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F13:K19"/>
-    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="B4:H4"/>
     <mergeCell ref="K24:K28"/>
     <mergeCell ref="L24:N28"/>
     <mergeCell ref="A21:N21"/>
@@ -6335,19 +6342,12 @@
     <mergeCell ref="A24:B28"/>
     <mergeCell ref="C24:E28"/>
     <mergeCell ref="A23:N23"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E19"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F13:K19"/>
+    <mergeCell ref="L16:L19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="L6">
